--- a/template/Device List.xlsx
+++ b/template/Device List.xlsx
@@ -637,7 +637,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T84"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr defaultRowHeight="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" customWidth="1"/>
@@ -801,14 +804,6 @@
       <c r="G12" s="7"/>
       <c r="H12" s="9"/>
       <c r="I12" s="12"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15"/>
     </row>
     <row r="13" spans="1:20" s="2" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
@@ -822,14 +817,6 @@
       <c r="G13" s="7"/>
       <c r="H13" s="9"/>
       <c r="I13" s="12"/>
-      <c r="M13" s="18"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
     </row>
     <row r="14" spans="1:20" s="2" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
@@ -843,14 +830,6 @@
       <c r="G14" s="7"/>
       <c r="H14" s="9"/>
       <c r="I14" s="12"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="17"/>
-      <c r="T14" s="17"/>
     </row>
     <row r="15" spans="1:20" s="2" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
@@ -864,14 +843,6 @@
       <c r="G15" s="7"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
     </row>
     <row r="16" spans="1:20" s="2" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
@@ -1772,21 +1743,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A3:I84" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="7">
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="S15:T15"/>
+  <mergeCells count="1">
     <mergeCell ref="D1:E1"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="S13:T13"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H13:I13" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"ICU,Inpatient,ER,NICU,OR,"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup scale="16" orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape" fitToHeight="0" r:id="rId1"/>
 </worksheet>
 </file>